--- a/output/2026-08-31_16_Italia_Emilia_Romagna_Cleaning.xlsx
+++ b/output/2026-08-31_16_Italia_Emilia_Romagna_Cleaning.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sede principale Via Europa 10/12/14, Sala Bolognese. Oltre 30 anni di attivita, famiglia Pasqua. Copre anche area Ferrara/Ravenna ma senza filiale fisica dedicata li (dedupe effettuato).</t>
+          <t>Sede principale Via Europa 10/12/14, Sala Bolognese. Oltre 30 anni di attivita, famiglia Pasqua. Copre anche area Ferrara/Ravenna ma senza filiale fisica dedicata li (dedupe effettuato). [DUPLICATO — vedi anche: 2026-08-31_13_Italia_Toscana_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Filiale fisica reale e distinta (Via Antonello Moroni, 90, Savignano sul Rubicone), showroom e magazzino ricambi.</t>
+          <t>Filiale fisica reale e distinta (Via Antonello Moroni, 90, Savignano sul Rubicone), showroom e magazzino ricambi. [DUPLICATO — vedi anche: 2026-08-31_13_Italia_Toscana_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -619,8 +619,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Via Emilia Ponente 20/3, Bologna. Confermata su piu directory di settore. Telefono/email non reperiti da fonti verificate.</t>
@@ -700,7 +698,6 @@
           <t>059 928589</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Attiva dal 1978, officina autorizzata ISTOBAL dal 2001, copre anche MO/RE/PR/BO/MN.</t>
@@ -822,7 +819,6 @@
           <t>059 820784</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Via Pedena Nord 49, Modena. Confermata su PagineBianche, MisterImprese, Kompass.</t>
@@ -1149,11 +1145,9 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Via Morgagni 64, Faenza. Filiale fisica reale confermata (2020), officina e magazzino ricambi. Contatti specifici sede non reperiti separatamente.</t>
+          <t>Via Morgagni 64, Faenza. Filiale fisica reale confermata (2020), officina e magazzino ricambi. Contatti specifici sede non reperiti separatamente. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1272,7 +1266,6 @@
           <t>0543 745228</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Via Emilia per Cesena 30, Forlimpopoli. P.IVA 01817300401 confermata.</t>
@@ -1352,7 +1345,6 @@
           <t>0523 1612000</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>ATTENZIONE: filiale/sede italiana del produttore multinazionale Nilfisk, non distributore terzo indipendente.</t>

--- a/output/2026-08-31_16_Italia_Emilia_Romagna_Cleaning.xlsx
+++ b/output/2026-08-31_16_Italia_Emilia_Romagna_Cleaning.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
